--- a/analysis/econometrics_outputs/sdid/Graficos/unemployment/sdid_levels_rf_top_vs_bottom.xlsx
+++ b/analysis/econometrics_outputs/sdid/Graficos/unemployment/sdid_levels_rf_top_vs_bottom.xlsx
@@ -507,13 +507,13 @@
         <v>7.104104754157772</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.08105629575484906</v>
+        <v>-0.05418327804577291</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05951426619556231</v>
+        <v>0.03264124848648616</v>
       </c>
     </row>
     <row r="3">
@@ -550,13 +550,13 @@
         <v>7.10792035462367</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.07797423427222915</v>
+        <v>-0.05110121656315299</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06259632767818223</v>
+        <v>0.03572330996910607</v>
       </c>
     </row>
     <row r="4">
@@ -593,13 +593,13 @@
         <v>7.094847165195247</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.07786791823332771</v>
+        <v>-0.05099490052425156</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06270264371708366</v>
+        <v>0.03582962600800751</v>
       </c>
     </row>
     <row r="5">
@@ -636,13 +636,13 @@
         <v>7.088243143403064</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0902664641145836</v>
+        <v>-0.06339344640550745</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05030409783582777</v>
+        <v>0.02343108012675162</v>
       </c>
     </row>
     <row r="6">
@@ -679,13 +679,13 @@
         <v>7.052152776892786</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.08811552098588814</v>
+        <v>-0.06124250327681199</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05245504096452323</v>
+        <v>0.02558202325544708</v>
       </c>
     </row>
     <row r="7">
@@ -722,13 +722,13 @@
         <v>7.013210098056684</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.08068726798014113</v>
+        <v>-0.05381425027106498</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05988329397027024</v>
+        <v>0.03301027626119409</v>
       </c>
     </row>
     <row r="8">
@@ -765,13 +765,13 @@
         <v>6.990393610697947</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0757850047023154</v>
+        <v>-0.04891198699323925</v>
       </c>
       <c r="K8" t="n">
-        <v>0.06478555724809597</v>
+        <v>0.03791253953901982</v>
       </c>
     </row>
     <row r="9">
@@ -808,13 +808,13 @@
         <v>6.993450342289484</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.07938091922181444</v>
+        <v>-0.05250790151273829</v>
       </c>
       <c r="K9" t="n">
-        <v>0.06118964272859694</v>
+        <v>0.03431662501952078</v>
       </c>
     </row>
     <row r="10">
@@ -851,13 +851,13 @@
         <v>6.961750846175582</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.08461646550154066</v>
+        <v>-0.05774344779246451</v>
       </c>
       <c r="K10" t="n">
-        <v>0.05595409644887071</v>
+        <v>0.02908107873979456</v>
       </c>
     </row>
     <row r="11">
@@ -894,13 +894,13 @@
         <v>6.940455356868366</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.08194887778105441</v>
+        <v>-0.05507586007197825</v>
       </c>
       <c r="K11" t="n">
-        <v>0.05862168416935697</v>
+        <v>0.03174866646028082</v>
       </c>
     </row>
     <row r="12">
@@ -937,13 +937,13 @@
         <v>6.899189937372787</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.06942105227472138</v>
+        <v>-0.04254803456564523</v>
       </c>
       <c r="K12" t="n">
-        <v>0.07114950967568999</v>
+        <v>0.04427649196661384</v>
       </c>
     </row>
     <row r="13">
@@ -980,13 +980,13 @@
         <v>6.890548614781523</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.09632995460045611</v>
+        <v>-0.06945693689137997</v>
       </c>
       <c r="K13" t="n">
-        <v>0.04424060734995526</v>
+        <v>0.01736758964087911</v>
       </c>
     </row>
     <row r="14">
@@ -1023,13 +1023,13 @@
         <v>6.872125403938335</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.07414668226140163</v>
+        <v>-0.04727366455232548</v>
       </c>
       <c r="K14" t="n">
-        <v>0.06642387968900974</v>
+        <v>0.03955086197993359</v>
       </c>
     </row>
     <row r="15">
@@ -1066,13 +1066,13 @@
         <v>6.863057023436981</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.08638173963702987</v>
+        <v>-0.05950872192795372</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0541888223133815</v>
+        <v>0.02731580460430535</v>
       </c>
     </row>
     <row r="16">
@@ -1109,13 +1109,13 @@
         <v>6.848255469596528</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.08269876050481149</v>
+        <v>-0.05582574279573534</v>
       </c>
       <c r="K16" t="n">
-        <v>0.05787180144559988</v>
+        <v>0.03099878373652373</v>
       </c>
     </row>
     <row r="17">
@@ -1152,13 +1152,13 @@
         <v>6.831796646509599</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.09043123139586727</v>
+        <v>-0.06355821368679113</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0501393305545441</v>
+        <v>0.02326631284546795</v>
       </c>
     </row>
     <row r="18">
@@ -1195,13 +1195,13 @@
         <v>6.797718219634423</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.07915774474529401</v>
+        <v>-0.05228472703621786</v>
       </c>
       <c r="K18" t="n">
-        <v>0.06141281720511736</v>
+        <v>0.03453979949604121</v>
       </c>
     </row>
     <row r="19">
@@ -1238,13 +1238,13 @@
         <v>6.799390427346465</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.09139113772893535</v>
+        <v>-0.06451812001985921</v>
       </c>
       <c r="K19" t="n">
-        <v>0.04917942422147602</v>
+        <v>0.02230640651239987</v>
       </c>
     </row>
     <row r="20">
@@ -1281,13 +1281,13 @@
         <v>6.822770687176849</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.07671889969810029</v>
+        <v>-0.04984588198902414</v>
       </c>
       <c r="K20" t="n">
-        <v>0.06385166225231108</v>
+        <v>0.03697864454323493</v>
       </c>
     </row>
     <row r="21">
@@ -1324,13 +1324,13 @@
         <v>6.835744690278347</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.07028528097520569</v>
+        <v>-0.04341226326612953</v>
       </c>
       <c r="K21" t="n">
-        <v>0.07028528097520569</v>
+        <v>0.04341226326612953</v>
       </c>
     </row>
     <row r="22">
@@ -1367,13 +1367,13 @@
         <v>6.821413116244982</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.07674438515364</v>
+        <v>-0.04987136744456385</v>
       </c>
       <c r="K22" t="n">
-        <v>0.06382617679677137</v>
+        <v>0.03695315908769522</v>
       </c>
     </row>
     <row r="23">
@@ -1410,13 +1410,13 @@
         <v>6.790401898638715</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.04871104315892059</v>
+        <v>-0.02183802544984444</v>
       </c>
       <c r="K23" t="n">
-        <v>0.09185951879149078</v>
+        <v>0.06498650108241463</v>
       </c>
     </row>
     <row r="24">
@@ -1453,13 +1453,13 @@
         <v>6.779227829185711</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0403627251009213</v>
+        <v>-0.01348970739184515</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1002078368494901</v>
+        <v>0.07333481914041393</v>
       </c>
     </row>
     <row r="25">
@@ -1496,13 +1496,13 @@
         <v>6.776069211136809</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.04709687974321917</v>
+        <v>-0.02022386203414302</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0934736822071922</v>
+        <v>0.06660066449811605</v>
       </c>
     </row>
     <row r="26">
@@ -1539,13 +1539,13 @@
         <v>6.780762678620708</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.02692063224176232</v>
+        <v>-4.761453268616739e-05</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1136499297086491</v>
+        <v>0.08677691199957291</v>
       </c>
     </row>
     <row r="27">
@@ -1582,13 +1582,13 @@
         <v>6.792076090761918</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.03281851749109842</v>
+        <v>-0.005945499782022266</v>
       </c>
       <c r="K27" t="n">
-        <v>0.107752044459313</v>
+        <v>0.08087902675023681</v>
       </c>
     </row>
     <row r="28">
@@ -1625,13 +1625,13 @@
         <v>6.75775757461444</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.01777462842968601</v>
+        <v>0.009098389279390141</v>
       </c>
       <c r="K28" t="n">
-        <v>0.1227959335207254</v>
+        <v>0.09592291581164922</v>
       </c>
     </row>
     <row r="29">
@@ -1668,13 +1668,13 @@
         <v>6.749134076144799</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.03179787827580481</v>
+        <v>-0.00492486056672866</v>
       </c>
       <c r="K29" t="n">
-        <v>0.1087726836746066</v>
+        <v>0.08189966596553042</v>
       </c>
     </row>
     <row r="30">
@@ -1711,13 +1711,13 @@
         <v>6.723695527402107</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.01508064260146623</v>
+        <v>0.01179237510760992</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1254899193489452</v>
+        <v>0.098616901639869</v>
       </c>
     </row>
     <row r="31">
@@ -1754,13 +1754,13 @@
         <v>6.698209916737529</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J31" t="n">
-        <v>0.01696867951176741</v>
+        <v>0.04384169722084356</v>
       </c>
       <c r="K31" t="n">
-        <v>0.1575392414621788</v>
+        <v>0.1306662237531026</v>
       </c>
     </row>
     <row r="32">
@@ -1797,13 +1797,13 @@
         <v>6.698692444359098</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J32" t="n">
-        <v>0.05215627499274091</v>
+        <v>0.07902929270181705</v>
       </c>
       <c r="K32" t="n">
-        <v>0.1927268369431523</v>
+        <v>0.1658538192340761</v>
       </c>
     </row>
     <row r="33">
@@ -1840,13 +1840,13 @@
         <v>6.68685069565933</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J33" t="n">
-        <v>0.08774997720310231</v>
+        <v>0.1146229949121784</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2283205391535137</v>
+        <v>0.2014475214444375</v>
       </c>
     </row>
     <row r="34">
@@ -1883,13 +1883,13 @@
         <v>6.685906837462171</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J34" t="n">
-        <v>0.08028370469631631</v>
+        <v>0.1071567224053925</v>
       </c>
       <c r="K34" t="n">
-        <v>0.2208542666467277</v>
+        <v>0.1939812489376515</v>
       </c>
     </row>
     <row r="35">
@@ -1926,13 +1926,13 @@
         <v>6.687680752212818</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J35" t="n">
-        <v>0.08759113453028379</v>
+        <v>0.1144641522393599</v>
       </c>
       <c r="K35" t="n">
-        <v>0.2281616964806952</v>
+        <v>0.201288678771619</v>
       </c>
     </row>
     <row r="36">
@@ -1969,13 +1969,13 @@
         <v>6.664957025168109</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J36" t="n">
-        <v>0.09730614758105306</v>
+        <v>0.1241791652901292</v>
       </c>
       <c r="K36" t="n">
-        <v>0.2378767095314644</v>
+        <v>0.2110036918223883</v>
       </c>
     </row>
     <row r="37">
@@ -2012,13 +2012,13 @@
         <v>6.664671274980567</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J37" t="n">
-        <v>0.08843926244603596</v>
+        <v>0.1153122801551121</v>
       </c>
       <c r="K37" t="n">
-        <v>0.2290098243964473</v>
+        <v>0.2021368066873712</v>
       </c>
     </row>
     <row r="38">
@@ -2055,13 +2055,13 @@
         <v>6.664156136901583</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J38" t="n">
-        <v>0.09966884183693493</v>
+        <v>0.1265418595460111</v>
       </c>
       <c r="K38" t="n">
-        <v>0.2402394037873463</v>
+        <v>0.2133663860782702</v>
       </c>
     </row>
     <row r="39">
@@ -2098,13 +2098,13 @@
         <v>6.666320069616966</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J39" t="n">
-        <v>0.084827293450368</v>
+        <v>0.1117003111594441</v>
       </c>
       <c r="K39" t="n">
-        <v>0.2253978554007794</v>
+        <v>0.1985248376917032</v>
       </c>
     </row>
     <row r="40">
@@ -2141,13 +2141,13 @@
         <v>6.657549651900565</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J40" t="n">
-        <v>0.09149707273995956</v>
+        <v>0.1183700904490357</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2320676346903709</v>
+        <v>0.2051946169812948</v>
       </c>
     </row>
     <row r="41">
@@ -2184,13 +2184,13 @@
         <v>6.636782061792481</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J41" t="n">
-        <v>0.08460326089411942</v>
+        <v>0.1114762786031956</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2251738228445308</v>
+        <v>0.1983008051354546</v>
       </c>
     </row>
     <row r="42">
@@ -2227,13 +2227,13 @@
         <v>6.615270197792756</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J42" t="n">
-        <v>0.09201038141986585</v>
+        <v>0.118883399128942</v>
       </c>
       <c r="K42" t="n">
-        <v>0.2325809433702772</v>
+        <v>0.2057079256612011</v>
       </c>
     </row>
     <row r="43">
@@ -2270,13 +2270,13 @@
         <v>6.586782091465081</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J43" t="n">
-        <v>0.1069305673489673</v>
+        <v>0.1338035850580435</v>
       </c>
       <c r="K43" t="n">
-        <v>0.2475011292993787</v>
+        <v>0.2206281115903026</v>
       </c>
     </row>
     <row r="44">
@@ -2313,13 +2313,13 @@
         <v>6.581272343148414</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J44" t="n">
-        <v>0.144292150057588</v>
+        <v>0.1711651677666642</v>
       </c>
       <c r="K44" t="n">
-        <v>0.2848627120079994</v>
+        <v>0.2579896942989232</v>
       </c>
     </row>
     <row r="45">
@@ -2356,13 +2356,13 @@
         <v>6.585511222646539</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J45" t="n">
-        <v>0.1641400934037673</v>
+        <v>0.1910131111128435</v>
       </c>
       <c r="K45" t="n">
-        <v>0.3047106553541787</v>
+        <v>0.2778376376451026</v>
       </c>
     </row>
     <row r="46">
@@ -2399,13 +2399,13 @@
         <v>6.578428794914376</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J46" t="n">
-        <v>0.1596256449506293</v>
+        <v>0.1864986626597054</v>
       </c>
       <c r="K46" t="n">
-        <v>0.3001962069010407</v>
+        <v>0.2733231891919645</v>
       </c>
     </row>
     <row r="47">
@@ -2442,13 +2442,13 @@
         <v>6.566274945836686</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J47" t="n">
-        <v>0.182107064404158</v>
+        <v>0.2089800821132342</v>
       </c>
       <c r="K47" t="n">
-        <v>0.3226776263545694</v>
+        <v>0.2958046086454932</v>
       </c>
     </row>
     <row r="48">
@@ -2485,13 +2485,13 @@
         <v>6.551311671142009</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J48" t="n">
-        <v>0.1934045574125947</v>
+        <v>0.2202775751216708</v>
       </c>
       <c r="K48" t="n">
-        <v>0.3339751193630061</v>
+        <v>0.3071021016539299</v>
       </c>
     </row>
     <row r="49">
@@ -2528,13 +2528,13 @@
         <v>6.559418988428153</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J49" t="n">
-        <v>0.1804850325742511</v>
+        <v>0.2073580502833272</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3210555945246625</v>
+        <v>0.2941825768155863</v>
       </c>
     </row>
     <row r="50">
@@ -2571,13 +2571,13 @@
         <v>6.556669530327039</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J50" t="n">
-        <v>0.1936278490109464</v>
+        <v>0.2205008667200226</v>
       </c>
       <c r="K50" t="n">
-        <v>0.3341984109613578</v>
+        <v>0.3073253932522816</v>
       </c>
     </row>
     <row r="51">
@@ -2614,13 +2614,13 @@
         <v>6.555228034605894</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J51" t="n">
-        <v>0.1913963916265413</v>
+        <v>0.2182694093356175</v>
       </c>
       <c r="K51" t="n">
-        <v>0.3319669535769527</v>
+        <v>0.3050939358678765</v>
       </c>
     </row>
     <row r="52">
@@ -2657,13 +2657,13 @@
         <v>6.528154921048175</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J52" t="n">
-        <v>0.2099605684290478</v>
+        <v>0.2368335861381239</v>
       </c>
       <c r="K52" t="n">
-        <v>0.3505311303794592</v>
+        <v>0.323658112670383</v>
       </c>
     </row>
     <row r="53">
@@ -2700,13 +2700,13 @@
         <v>6.496261491598052</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J53" t="n">
-        <v>0.2187730077168377</v>
+        <v>0.2456460254259139</v>
       </c>
       <c r="K53" t="n">
-        <v>0.3593435696672491</v>
+        <v>0.3324705519581729</v>
       </c>
     </row>
     <row r="54">
@@ -2743,13 +2743,13 @@
         <v>6.481536648896927</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J54" t="n">
-        <v>0.2145401818666823</v>
+        <v>0.2414131995757585</v>
       </c>
       <c r="K54" t="n">
-        <v>0.3551107438170937</v>
+        <v>0.3282377261080175</v>
       </c>
     </row>
     <row r="55">
@@ -2786,13 +2786,13 @@
         <v>6.489343326176617</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J55" t="n">
-        <v>0.1996625452988774</v>
+        <v>0.2265355630079535</v>
       </c>
       <c r="K55" t="n">
-        <v>0.3402331072492888</v>
+        <v>0.3133600895402126</v>
       </c>
     </row>
     <row r="56">
@@ -2829,13 +2829,13 @@
         <v>6.475050863910019</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J56" t="n">
-        <v>0.2510131334832961</v>
+        <v>0.2778861511923723</v>
       </c>
       <c r="K56" t="n">
-        <v>0.3915836954337075</v>
+        <v>0.3647106777246313</v>
       </c>
     </row>
     <row r="57">
@@ -2872,13 +2872,13 @@
         <v>6.480369723341155</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J57" t="n">
-        <v>0.266431694307218</v>
+        <v>0.2933047120162942</v>
       </c>
       <c r="K57" t="n">
-        <v>0.4070022562576294</v>
+        <v>0.3801292385485532</v>
       </c>
     </row>
     <row r="58">
@@ -2915,13 +2915,13 @@
         <v>6.46160694902343</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J58" t="n">
-        <v>0.2703495757826204</v>
+        <v>0.2972225934916966</v>
       </c>
       <c r="K58" t="n">
-        <v>0.4109201377330318</v>
+        <v>0.3840471200239556</v>
       </c>
     </row>
     <row r="59">
@@ -2958,13 +2958,13 @@
         <v>6.474272617585278</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J59" t="n">
-        <v>0.2680011919759668</v>
+        <v>0.294874209685043</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4085717539263782</v>
+        <v>0.381698736217302</v>
       </c>
     </row>
     <row r="60">
@@ -3001,13 +3001,13 @@
         <v>6.478768998562764</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J60" t="n">
-        <v>0.2561123349776973</v>
+        <v>0.2829853526867734</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3966828969281087</v>
+        <v>0.3698098792190325</v>
       </c>
     </row>
     <row r="61">
@@ -3044,13 +3044,13 @@
         <v>6.47954832512137</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J61" t="n">
-        <v>0.2515352784390326</v>
+        <v>0.2784082961481087</v>
       </c>
       <c r="K61" t="n">
-        <v>0.392105840389444</v>
+        <v>0.3652328226803678</v>
       </c>
     </row>
     <row r="62">
@@ -3087,13 +3087,13 @@
         <v>6.460273892219845</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J62" t="n">
-        <v>0.27837478416304</v>
+        <v>0.3052478018721161</v>
       </c>
       <c r="K62" t="n">
-        <v>0.4189453461134514</v>
+        <v>0.3920723284043752</v>
       </c>
     </row>
     <row r="63">
@@ -3130,13 +3130,13 @@
         <v>6.482676574537051</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J63" t="n">
-        <v>0.2551809749827829</v>
+        <v>0.2820539926918591</v>
       </c>
       <c r="K63" t="n">
-        <v>0.3957515369331943</v>
+        <v>0.3688785192241181</v>
       </c>
     </row>
     <row r="64">
@@ -3173,13 +3173,13 @@
         <v>6.444468361480665</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0358598372322478</v>
+        <v>0.02214911391129058</v>
       </c>
       <c r="J64" t="n">
-        <v>0.292551056197164</v>
+        <v>0.3194240739062402</v>
       </c>
       <c r="K64" t="n">
-        <v>0.4331216181475754</v>
+        <v>0.4062486004384993</v>
       </c>
     </row>
   </sheetData>
